--- a/ig/homecareobservation/StructureDefinition-medcom-homecareobservation-message.xlsx
+++ b/ig/homecareobservation/StructureDefinition-medcom-homecareobservation-message.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.1</t>
+    <t>1.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-19T07:53:40+00:00</t>
+    <t>2026-06-03T08:12:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1453,7 +1453,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>85</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>121</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>130</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>174</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>188</v>
       </c>
@@ -6783,12 +6783,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN49">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
